--- a/Extension/New data/CP_results.xlsx
+++ b/Extension/New data/CP_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sfolk\L3PPP\Extension\New data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30E5197E-7906-4B0B-A68E-6420E2794CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BFE8C48-1155-4B39-BD6C-DB070CA309E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{233CAA3C-2DF9-4868-852D-9F2BF2D68E0B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{233CAA3C-2DF9-4868-852D-9F2BF2D68E0B}"/>
   </bookViews>
   <sheets>
     <sheet name="1D" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="36">
   <si>
     <t>Flat_wide</t>
   </si>
@@ -183,11 +183,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -574,22 +571,22 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.72750000000000004</v>
+        <v>0.72789999999999999</v>
       </c>
       <c r="D3">
-        <v>-1.291E-2</v>
+        <v>-1.2749999999999999E-2</v>
       </c>
       <c r="E3">
-        <v>1.247E-2</v>
+        <v>1.2409999999999999E-2</v>
       </c>
       <c r="G3">
-        <v>0.80500000000000005</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="H3">
-        <v>1.6352000000000001E-4</v>
+        <v>1.6178000000000001E-4</v>
       </c>
       <c r="I3">
-        <v>25.245867629999999</v>
+        <v>22.957966679999998</v>
       </c>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.3">
@@ -597,178 +594,135 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>0.72740000000000005</v>
+        <v>0.72729999999999995</v>
       </c>
       <c r="D4">
-        <v>-1.257E-2</v>
+        <v>-1.299E-2</v>
       </c>
       <c r="E4">
-        <v>1.274E-2</v>
+        <v>1.286E-2</v>
       </c>
       <c r="G4">
-        <v>0.80500000000000005</v>
+        <v>0.80400000000000005</v>
       </c>
       <c r="H4">
-        <v>1.6346000000000001E-4</v>
+        <v>1.674E-4</v>
       </c>
       <c r="I4">
-        <v>21.822081399999998</v>
-      </c>
-    </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>0.72619999999999996</v>
-      </c>
-      <c r="D5">
-        <v>-1.268E-2</v>
-      </c>
-      <c r="E5">
-        <v>1.244E-2</v>
-      </c>
-      <c r="G5">
-        <v>0.80800000000000005</v>
-      </c>
-      <c r="H5">
-        <v>1.5924999999999999E-4</v>
-      </c>
-      <c r="I5">
-        <v>22.494851430000001</v>
+        <v>25.981015960000001</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6">
-        <v>0.69530000000000003</v>
-      </c>
-      <c r="D6">
-        <v>-6.2310000000000004E-3</v>
-      </c>
-      <c r="E6">
-        <v>6.398E-3</v>
-      </c>
-      <c r="G6">
-        <v>0.80500000000000005</v>
-      </c>
-      <c r="H6" s="2">
-        <v>4.0077999999999998E-5</v>
-      </c>
-      <c r="I6">
-        <v>24.976747830000001</v>
-      </c>
+      <c r="H6" s="1"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="R13" s="2"/>
+      <c r="R13" s="1"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="R14" s="2"/>
+      <c r="R14" s="1"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="R15" s="2"/>
+      <c r="R15" s="1"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
     </row>
     <row r="20" spans="16:31" x14ac:dyDescent="0.3">
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="4"/>
-      <c r="AA20" s="4"/>
-      <c r="AC20" s="4"/>
-      <c r="AD20" s="4"/>
-      <c r="AE20" s="4"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
     </row>
     <row r="21" spans="16:31" x14ac:dyDescent="0.3">
-      <c r="T21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
+      <c r="T21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="16:31" x14ac:dyDescent="0.3">
-      <c r="R22" s="2"/>
-      <c r="AB22" s="2"/>
+      <c r="R22" s="1"/>
+      <c r="AB22" s="1"/>
     </row>
     <row r="23" spans="16:31" x14ac:dyDescent="0.3">
-      <c r="AB23" s="2"/>
+      <c r="AB23" s="1"/>
     </row>
     <row r="24" spans="16:31" x14ac:dyDescent="0.3">
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
     </row>
     <row r="27" spans="16:31" x14ac:dyDescent="0.3">
-      <c r="T27" s="2"/>
+      <c r="T27" s="1"/>
     </row>
     <row r="28" spans="16:31" x14ac:dyDescent="0.3">
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
     </row>
     <row r="30" spans="16:31" x14ac:dyDescent="0.3">
-      <c r="S30" s="2"/>
+      <c r="S30" s="1"/>
     </row>
     <row r="31" spans="16:31" x14ac:dyDescent="0.3">
-      <c r="S31" s="2"/>
+      <c r="S31" s="1"/>
     </row>
     <row r="32" spans="16:31" x14ac:dyDescent="0.3">
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
     </row>
     <row r="33" spans="16:19" x14ac:dyDescent="0.3">
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
     </row>
     <row r="34" spans="16:19" x14ac:dyDescent="0.3">
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
     </row>
     <row r="35" spans="16:19" x14ac:dyDescent="0.3">
-      <c r="S35" s="2"/>
+      <c r="S35" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -828,23 +782,23 @@
       <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="1"/>
+      <c r="Q2" s="3"/>
       <c r="R2" t="s">
         <v>11</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="1"/>
+      <c r="T2" s="3"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
@@ -854,49 +808,49 @@
         <v>0.70760000000000001</v>
       </c>
       <c r="D3">
-        <v>-1.8769999999999998E-2</v>
+        <v>-1.8800000000000001E-2</v>
       </c>
       <c r="E3">
-        <v>1.8110000000000001E-2</v>
+        <v>1.84E-2</v>
       </c>
       <c r="G3">
         <v>69.53</v>
       </c>
       <c r="H3">
-        <v>-0.30180000000000001</v>
+        <v>-0.30359999999999998</v>
       </c>
       <c r="I3">
-        <v>0.29909999999999998</v>
+        <v>0.3034</v>
       </c>
       <c r="K3">
         <v>0.71499999999999997</v>
       </c>
       <c r="L3">
-        <v>3.4660000000000002E-4</v>
+        <v>3.4987000000000001E-4</v>
       </c>
       <c r="M3">
-        <v>4.0152800000000004E-3</v>
+        <v>4.0623999999999999E-3</v>
       </c>
       <c r="N3">
-        <v>4.0152800000000004E-3</v>
+        <v>4.0623999999999999E-3</v>
       </c>
       <c r="O3">
-        <v>9.2495129999999995E-2</v>
+        <v>9.2984769999999994E-2</v>
       </c>
       <c r="P3">
-        <v>1.7197E-4</v>
+        <v>1.7206E-4</v>
       </c>
       <c r="Q3">
-        <v>9.2669760000000004E-2</v>
-      </c>
-      <c r="R3" s="2">
+        <v>9.3162579999999995E-2</v>
+      </c>
+      <c r="R3" s="1">
         <v>540</v>
       </c>
       <c r="S3">
-        <v>31.049476720000001</v>
+        <v>28.045503220000001</v>
       </c>
       <c r="T3">
-        <v>30.390334549999999</v>
+        <v>27.567859599999998</v>
       </c>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.3">
@@ -904,52 +858,52 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>0.70789999999999997</v>
+        <v>0.70720000000000005</v>
       </c>
       <c r="D4">
-        <v>-1.8960000000000001E-2</v>
+        <v>-1.882E-2</v>
       </c>
       <c r="E4">
-        <v>1.8319999999999999E-2</v>
+        <v>1.839E-2</v>
       </c>
       <c r="G4">
         <v>69.53</v>
       </c>
       <c r="H4">
-        <v>-0.30170000000000002</v>
+        <v>-0.30159999999999998</v>
       </c>
       <c r="I4">
-        <v>0.3034</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="K4">
         <v>0.71499999999999997</v>
       </c>
       <c r="L4">
-        <v>3.548E-4</v>
+        <v>3.5107999999999998E-4</v>
       </c>
       <c r="M4">
-        <v>4.11642E-3</v>
+        <v>4.0195700000000001E-3</v>
       </c>
       <c r="N4">
-        <v>4.11642E-3</v>
+        <v>4.0195700000000001E-3</v>
       </c>
       <c r="O4">
-        <v>9.2969410000000002E-2</v>
+        <v>9.192082E-2</v>
       </c>
       <c r="P4">
-        <v>1.7220000000000001E-4</v>
+        <v>1.7496999999999999E-4</v>
       </c>
       <c r="Q4">
-        <v>9.3152009999999993E-2</v>
-      </c>
-      <c r="R4" s="2">
-        <v>540</v>
+        <v>9.2096919999999999E-2</v>
+      </c>
+      <c r="R4" s="1">
+        <v>530</v>
       </c>
       <c r="S4">
-        <v>30.95488924</v>
+        <v>28.366975180000001</v>
       </c>
       <c r="T4">
-        <v>30.07230199</v>
+        <v>29.432258640000001</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.3">
@@ -957,52 +911,52 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>0.70589999999999997</v>
+        <v>0.70189999999999997</v>
       </c>
       <c r="D5">
-        <v>-1.8540000000000001E-2</v>
+        <v>-1.6580000000000001E-2</v>
       </c>
       <c r="E5">
-        <v>1.7670000000000002E-2</v>
+        <v>1.6420000000000001E-2</v>
       </c>
       <c r="G5">
-        <v>69.510000000000005</v>
+        <v>69.45</v>
       </c>
       <c r="H5">
-        <v>-0.29980000000000001</v>
+        <v>-0.28310000000000002</v>
       </c>
       <c r="I5">
-        <v>0.30070000000000002</v>
+        <v>0.2843</v>
       </c>
       <c r="K5">
-        <v>0.71299999999999997</v>
+        <v>0.71499999999999997</v>
       </c>
       <c r="L5">
-        <v>3.3053999999999999E-4</v>
+        <v>2.7730000000000002E-4</v>
       </c>
       <c r="M5">
-        <v>3.8278600000000002E-3</v>
+        <v>3.1389199999999999E-3</v>
       </c>
       <c r="N5">
-        <v>3.8278600000000002E-3</v>
+        <v>3.1389199999999999E-3</v>
       </c>
       <c r="O5">
-        <v>9.0640689999999996E-2</v>
+        <v>8.1426059999999995E-2</v>
       </c>
       <c r="P5">
-        <v>1.6857999999999999E-4</v>
+        <v>1.5606999999999999E-4</v>
       </c>
       <c r="Q5">
-        <v>9.0802640000000004E-2</v>
-      </c>
-      <c r="R5" s="2">
-        <v>540</v>
+        <v>8.1547300000000003E-2</v>
+      </c>
+      <c r="R5" s="1">
+        <v>520</v>
       </c>
       <c r="S5">
-        <v>29.17819596</v>
+        <v>30.107426100000001</v>
       </c>
       <c r="T5">
-        <v>29.46733618</v>
+        <v>29.928084420000001</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
@@ -1010,130 +964,135 @@
         <v>20</v>
       </c>
       <c r="C6">
-        <v>0.68810000000000004</v>
+        <v>0.70469999999999999</v>
       </c>
       <c r="D6">
-        <v>-6.7099999999999998E-3</v>
+        <v>-6.607E-3</v>
       </c>
       <c r="E6">
-        <v>6.7219999999999997E-3</v>
+        <v>6.6579999999999999E-3</v>
       </c>
       <c r="G6">
-        <v>69.3</v>
+        <v>69.489999999999995</v>
       </c>
       <c r="H6">
-        <v>-0.2253</v>
+        <v>-0.25280000000000002</v>
       </c>
       <c r="I6">
-        <v>0.2238</v>
+        <v>0.25430000000000003</v>
       </c>
       <c r="K6">
-        <v>0.71299999999999997</v>
-      </c>
-      <c r="L6" s="2">
-        <v>4.5239470200000001E-5</v>
-      </c>
-      <c r="M6" s="2">
-        <v>5.2356299800000001E-4</v>
-      </c>
-      <c r="N6" s="2">
-        <v>5.2356299800000001E-4</v>
-      </c>
-      <c r="O6" s="2">
-        <v>5.1550093200000001E-2</v>
-      </c>
-      <c r="P6" s="2">
-        <v>3.9917837899999998E-5</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>5.1555414799999998E-2</v>
-      </c>
-      <c r="R6" s="2">
-        <v>1300</v>
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="L6" s="1">
+        <v>4.42089473E-5</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1.12294879E-3</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1.12294879E-3</v>
+      </c>
+      <c r="O6" s="1">
+        <v>6.4405553199999993E-2</v>
+      </c>
+      <c r="P6" s="1">
+        <v>2.46221851E-5</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>6.4425139899999997E-2</v>
+      </c>
+      <c r="R6" s="1">
+        <v>2600</v>
       </c>
       <c r="S6">
-        <v>29.302551359999999</v>
+        <v>28.036858030000001</v>
       </c>
       <c r="T6">
-        <v>29.72502296</v>
+        <v>29.248545719999999</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="T11" s="2"/>
+      <c r="T11" s="1"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="R12" s="2"/>
+      <c r="R12" s="1"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
     </row>
     <row r="17" spans="16:28" x14ac:dyDescent="0.3">
-      <c r="T17" s="2"/>
+      <c r="T17" s="1"/>
     </row>
     <row r="21" spans="16:28" x14ac:dyDescent="0.3">
-      <c r="T21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
+      <c r="T21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="16:28" x14ac:dyDescent="0.3">
-      <c r="R22" s="2"/>
-      <c r="AB22" s="2"/>
+      <c r="R22" s="1"/>
+      <c r="AB22" s="1"/>
     </row>
     <row r="23" spans="16:28" x14ac:dyDescent="0.3">
-      <c r="AB23" s="2"/>
+      <c r="AB23" s="1"/>
     </row>
     <row r="24" spans="16:28" x14ac:dyDescent="0.3">
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
     </row>
     <row r="27" spans="16:28" x14ac:dyDescent="0.3">
-      <c r="T27" s="2"/>
+      <c r="T27" s="1"/>
     </row>
     <row r="30" spans="16:28" x14ac:dyDescent="0.3">
-      <c r="S30" s="2"/>
+      <c r="S30" s="1"/>
     </row>
     <row r="31" spans="16:28" x14ac:dyDescent="0.3">
-      <c r="S31" s="2"/>
+      <c r="S31" s="1"/>
     </row>
     <row r="32" spans="16:28" x14ac:dyDescent="0.3">
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
     </row>
     <row r="33" spans="16:19" x14ac:dyDescent="0.3">
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
     </row>
     <row r="34" spans="16:19" x14ac:dyDescent="0.3">
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
     </row>
     <row r="35" spans="16:19" x14ac:dyDescent="0.3">
-      <c r="S35" s="2"/>
+      <c r="S35" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="S2:T2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1191,112 +1150,112 @@
       <c r="O2" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1" t="s">
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
       <c r="AB2" t="s">
         <v>11</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AC2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
     </row>
     <row r="3" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.69699999999999995</v>
+        <v>0.69920000000000004</v>
       </c>
       <c r="D3">
-        <v>-0.1129</v>
+        <v>-0.11459999999999999</v>
       </c>
       <c r="E3">
-        <v>0.1087</v>
+        <v>0.1085</v>
       </c>
       <c r="G3">
         <v>69.510000000000005</v>
       </c>
       <c r="H3">
-        <v>-0.37959999999999999</v>
+        <v>-0.3805</v>
       </c>
       <c r="I3">
-        <v>0.37230000000000002</v>
+        <v>0.374</v>
       </c>
       <c r="K3">
-        <v>1.6629999999999999E-2</v>
+        <v>1.3169999999999999E-2</v>
       </c>
       <c r="L3">
         <v>-0.1716</v>
       </c>
       <c r="M3">
-        <v>0.17879999999999999</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="O3">
         <v>0.64600000000000002</v>
       </c>
       <c r="P3">
-        <v>1.2429620000000001E-2</v>
+        <v>1.2577980000000001E-2</v>
       </c>
       <c r="Q3">
-        <v>-1.9384160000000001E-2</v>
+        <v>-1.9625030000000002E-2</v>
       </c>
       <c r="R3">
-        <v>2.8782789999999999E-2</v>
+        <v>2.8812310000000001E-2</v>
       </c>
       <c r="S3">
-        <v>-1.9384160000000001E-2</v>
-      </c>
-      <c r="T3" s="2">
-        <v>3.1110570000000001E-2</v>
+        <v>-1.9625030000000002E-2</v>
+      </c>
+      <c r="T3" s="1">
+        <v>3.1492350000000002E-2</v>
       </c>
       <c r="U3">
-        <v>-3.9696259999999997E-2</v>
+        <v>-3.9769649999999997E-2</v>
       </c>
       <c r="V3">
-        <v>2.8782789999999999E-2</v>
+        <v>2.8812310000000001E-2</v>
       </c>
       <c r="W3">
-        <v>-3.9696259999999997E-2</v>
+        <v>-3.9769649999999997E-2</v>
       </c>
       <c r="X3">
-        <v>0.14395826</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>1.3282875799999999E-4</v>
-      </c>
-      <c r="Z3" s="2">
-        <v>2.34924868E-2</v>
-      </c>
-      <c r="AA3" s="2">
-        <v>0.163873134</v>
-      </c>
-      <c r="AB3" s="2">
+        <v>0.14338797</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>1.3113455299999999E-4</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>2.3813152099999998E-2</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0.16351400799999999</v>
+      </c>
+      <c r="AB3" s="1">
         <v>1200</v>
       </c>
       <c r="AC3">
-        <v>33.818032819999999</v>
+        <v>36.429735280000003</v>
       </c>
       <c r="AD3">
-        <v>34.153594140000003</v>
+        <v>36.799960480000003</v>
       </c>
       <c r="AE3">
-        <v>34.491021629999999</v>
+        <v>34.208509849999999</v>
       </c>
     </row>
     <row r="4" spans="2:31" x14ac:dyDescent="0.3">
@@ -1304,311 +1263,168 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>0.70069999999999999</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="D4">
-        <v>-6.3E-2</v>
+        <v>-6.3630000000000006E-2</v>
       </c>
       <c r="E4">
-        <v>6.2740000000000004E-2</v>
+        <v>6.1679999999999999E-2</v>
       </c>
       <c r="G4">
         <v>69.52</v>
       </c>
       <c r="H4">
-        <v>-0.29930000000000001</v>
+        <v>-0.30349999999999999</v>
       </c>
       <c r="I4">
-        <v>0.30509999999999998</v>
+        <v>0.3024</v>
       </c>
       <c r="K4">
-        <v>1.141E-2</v>
+        <v>9.0939999999999997E-3</v>
       </c>
       <c r="L4">
-        <v>-0.10009999999999999</v>
+        <v>-9.8159999999999997E-2</v>
       </c>
       <c r="M4">
-        <v>9.9489999999999995E-2</v>
+        <v>0.10009999999999999</v>
       </c>
       <c r="O4">
         <v>0.61299999999999999</v>
       </c>
       <c r="P4">
-        <v>2.9622400000000001E-3</v>
+        <v>2.9544900000000002E-3</v>
       </c>
       <c r="Q4">
-        <v>-4.5955600000000003E-3</v>
-      </c>
-      <c r="R4" s="2">
-        <v>7.0791099999999996E-3</v>
+        <v>-4.5561600000000001E-3</v>
+      </c>
+      <c r="R4" s="1">
+        <v>7.2304300000000004E-3</v>
       </c>
       <c r="S4">
-        <v>-4.5955600000000003E-3</v>
+        <v>-4.5561600000000001E-3</v>
       </c>
       <c r="T4">
-        <v>7.9922699999999992E-3</v>
+        <v>7.8842300000000008E-3</v>
       </c>
       <c r="U4">
-        <v>-5.8902399999999997E-3</v>
+        <v>-6.0962400000000002E-3</v>
       </c>
       <c r="V4">
-        <v>7.0791099999999996E-3</v>
+        <v>7.2304300000000004E-3</v>
       </c>
       <c r="W4">
-        <v>-5.8902399999999997E-3</v>
+        <v>-6.0962400000000002E-3</v>
       </c>
       <c r="X4">
-        <v>9.2510330000000002E-2</v>
+        <v>9.2966989999999999E-2</v>
       </c>
       <c r="Y4">
-        <v>1.2679E-4</v>
+        <v>1.2711999999999999E-4</v>
       </c>
       <c r="Z4">
-        <v>9.8164600000000008E-3</v>
+        <v>9.6521200000000001E-3</v>
       </c>
       <c r="AA4">
-        <v>9.3521599999999996E-2</v>
-      </c>
-      <c r="AB4" s="2">
+        <v>9.4026460000000006E-2</v>
+      </c>
+      <c r="AB4" s="1">
         <v>740</v>
       </c>
       <c r="AC4">
-        <v>43.82453254</v>
+        <v>42.736237279999997</v>
       </c>
       <c r="AD4">
-        <v>43.124930159999998</v>
+        <v>41.694808610000003</v>
       </c>
       <c r="AE4">
-        <v>39.728941050000003</v>
+        <v>40.38563087</v>
       </c>
     </row>
     <row r="5" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>0.70489999999999997</v>
-      </c>
-      <c r="D5">
-        <v>-2.103E-2</v>
-      </c>
-      <c r="E5">
-        <v>2.0930000000000001E-2</v>
-      </c>
-      <c r="G5">
-        <v>69.510000000000005</v>
-      </c>
-      <c r="H5">
-        <v>-0.2989</v>
-      </c>
-      <c r="I5">
-        <v>0.3014</v>
-      </c>
-      <c r="K5">
-        <v>1.9170000000000001E-3</v>
-      </c>
-      <c r="L5">
-        <v>-1.839E-2</v>
-      </c>
-      <c r="M5">
-        <v>1.8489999999999999E-2</v>
-      </c>
-      <c r="O5">
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="P5">
-        <v>4.482E-4</v>
-      </c>
-      <c r="Q5">
-        <v>-2.0141000000000001E-4</v>
-      </c>
-      <c r="R5">
-        <v>3.97635E-3</v>
-      </c>
-      <c r="S5">
-        <v>-2.0141000000000001E-4</v>
-      </c>
-      <c r="T5">
-        <v>3.4527000000000001E-4</v>
-      </c>
-      <c r="U5">
-        <v>-2.8289E-4</v>
-      </c>
-      <c r="V5">
-        <v>3.97635E-3</v>
-      </c>
-      <c r="W5">
-        <v>-2.8289E-4</v>
-      </c>
-      <c r="X5">
-        <v>9.1268849999999999E-2</v>
-      </c>
-      <c r="Y5">
-        <v>1.1731999999999999E-4</v>
-      </c>
-      <c r="Z5">
-        <v>5.0146000000000001E-4</v>
-      </c>
-      <c r="AA5">
-        <v>9.1443549999999998E-2</v>
-      </c>
-      <c r="AB5" s="2">
-        <v>780</v>
-      </c>
-      <c r="AC5">
-        <v>34.701338139999997</v>
-      </c>
-      <c r="AD5">
-        <v>35.226164130000001</v>
-      </c>
-      <c r="AE5">
-        <v>36.033167769999999</v>
-      </c>
+      <c r="AB5" s="1"/>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6">
-        <v>0.68920000000000003</v>
-      </c>
-      <c r="D6">
-        <v>-8.3280000000000003E-3</v>
-      </c>
-      <c r="E6">
-        <v>8.3879999999999996E-3</v>
-      </c>
-      <c r="G6">
-        <v>69.31</v>
-      </c>
-      <c r="H6">
-        <v>-0.22650000000000001</v>
-      </c>
-      <c r="I6">
-        <v>0.22639999999999999</v>
-      </c>
-      <c r="K6">
-        <v>-1.629E-3</v>
-      </c>
-      <c r="L6">
-        <v>-7.9579999999999998E-3</v>
-      </c>
-      <c r="M6">
-        <v>8.0090000000000005E-3</v>
-      </c>
-      <c r="O6">
-        <v>0.64700000000000002</v>
-      </c>
-      <c r="P6" s="2">
-        <v>7.0088015399999998E-5</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>-4.0626418500000002E-5</v>
-      </c>
-      <c r="R6" s="2">
-        <v>5.9819522600000001E-4</v>
-      </c>
-      <c r="S6" s="2">
-        <v>-4.0626418500000002E-5</v>
-      </c>
-      <c r="T6" s="2">
-        <v>6.4224301599999993E-5</v>
-      </c>
-      <c r="U6" s="2">
-        <v>-1.5199525599999999E-4</v>
-      </c>
-      <c r="V6" s="2">
-        <v>5.9819522600000001E-4</v>
-      </c>
-      <c r="W6" s="2">
-        <v>-1.5199525599999999E-4</v>
-      </c>
-      <c r="X6" s="2">
-        <v>5.2064457000000001E-2</v>
-      </c>
-      <c r="Y6" s="2">
-        <v>2.4615796899999999E-5</v>
-      </c>
-      <c r="Z6" s="2">
-        <v>1.0236830200000001E-4</v>
-      </c>
-      <c r="AA6" s="2">
-        <v>5.2071785199999998E-2</v>
-      </c>
-      <c r="AB6" s="2">
-        <v>2100</v>
-      </c>
-      <c r="AC6">
-        <v>35.479882080000003</v>
-      </c>
-      <c r="AD6">
-        <v>35.351004719999999</v>
-      </c>
-      <c r="AE6">
-        <v>34.772582890000002</v>
-      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
     </row>
     <row r="9" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="T9" s="2"/>
+      <c r="T9" s="1"/>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="S12" s="2"/>
+      <c r="S12" s="1"/>
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="S13" s="2"/>
+      <c r="S13" s="1"/>
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.3">
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
     </row>
     <row r="17" spans="16:20" x14ac:dyDescent="0.3">
-      <c r="S17" s="2"/>
+      <c r="S17" s="1"/>
     </row>
     <row r="27" spans="16:20" x14ac:dyDescent="0.3">
-      <c r="T27" s="2"/>
+      <c r="T27" s="1"/>
     </row>
     <row r="30" spans="16:20" x14ac:dyDescent="0.3">
-      <c r="S30" s="2"/>
+      <c r="S30" s="1"/>
     </row>
     <row r="31" spans="16:20" x14ac:dyDescent="0.3">
-      <c r="S31" s="2"/>
+      <c r="S31" s="1"/>
     </row>
     <row r="32" spans="16:20" x14ac:dyDescent="0.3">
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
     </row>
     <row r="33" spans="16:19" x14ac:dyDescent="0.3">
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
     </row>
     <row r="34" spans="16:19" x14ac:dyDescent="0.3">
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
     </row>
     <row r="35" spans="16:19" x14ac:dyDescent="0.3">
-      <c r="S35" s="2"/>
+      <c r="S35" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="P2:X2"/>
+    <mergeCell ref="Y2:AA2"/>
+    <mergeCell ref="AC2:AE2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1633,10 +1449,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="T1" s="2"/>
+      <c r="T1" s="1"/>
     </row>
     <row r="2" spans="2:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C2" t="s">
@@ -1669,11 +1485,11 @@
       <c r="O2" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
       <c r="S2" t="s">
         <v>11</v>
       </c>
@@ -1689,50 +1505,50 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>0.80659999999999998</v>
+        <v>0.81140000000000001</v>
       </c>
       <c r="D3">
-        <v>-0.39029999999999998</v>
+        <v>-0.39789999999999998</v>
       </c>
       <c r="E3">
-        <v>0.34810000000000002</v>
+        <v>0.33689999999999998</v>
       </c>
       <c r="G3">
-        <v>69.53</v>
+        <v>69.540000000000006</v>
       </c>
       <c r="H3">
-        <v>-0.59240000000000004</v>
+        <v>-0.59960000000000002</v>
       </c>
       <c r="I3">
-        <v>0.58430000000000004</v>
+        <v>0.59860000000000002</v>
       </c>
       <c r="K3">
-        <v>-0.30930000000000002</v>
+        <v>-0.31109999999999999</v>
       </c>
       <c r="L3">
-        <v>-0.46189999999999998</v>
+        <v>-0.45700000000000002</v>
       </c>
       <c r="M3">
-        <v>0.56459999999999999</v>
+        <v>0.56010000000000004</v>
       </c>
       <c r="O3">
-        <v>0.58599999999999997</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="P3">
-        <v>1.483309E-2</v>
+        <v>1.498566E-2</v>
       </c>
       <c r="Q3">
-        <v>0.18556977999999999</v>
+        <v>0.18909234999999999</v>
       </c>
       <c r="R3">
-        <v>0.47073828000000001</v>
+        <v>0.48080638999999997</v>
       </c>
       <c r="S3">
         <v>32</v>
       </c>
       <c r="T3">
-        <f>(41.95304201+48.0207947+41.17707056)/3</f>
-        <v>43.716969089999999</v>
+        <f>(39.85510002+45.43980502+38.95142355)/3</f>
+        <v>41.415442863333332</v>
       </c>
       <c r="U3">
         <v>286</v>
@@ -1743,50 +1559,50 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>0.85260000000000002</v>
+        <v>0.8458</v>
       </c>
       <c r="D4">
-        <v>-0.26960000000000001</v>
+        <v>-0.26650000000000001</v>
       </c>
       <c r="E4">
-        <v>0.20619999999999999</v>
+        <v>0.20930000000000001</v>
       </c>
       <c r="G4">
-        <v>69.540000000000006</v>
+        <v>69.53</v>
       </c>
       <c r="H4">
-        <v>-0.40350000000000003</v>
+        <v>-0.40810000000000002</v>
       </c>
       <c r="I4">
-        <v>0.40360000000000001</v>
+        <v>0.39429999999999998</v>
       </c>
       <c r="K4">
-        <v>-0.36909999999999998</v>
+        <v>-0.35110000000000002</v>
       </c>
       <c r="L4">
-        <v>-0.43990000000000001</v>
+        <v>-0.4506</v>
       </c>
       <c r="M4">
-        <v>0.57909999999999995</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="O4">
-        <v>0.60499999999999998</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="P4">
-        <v>7.5177999999999996E-4</v>
+        <v>7.5863000000000005E-4</v>
       </c>
       <c r="Q4">
-        <v>0.12030357</v>
+        <v>0.11855607</v>
       </c>
       <c r="R4">
-        <v>0.28658117999999999</v>
-      </c>
-      <c r="S4" s="2">
+        <v>0.28801610999999999</v>
+      </c>
+      <c r="S4" s="1">
         <v>380</v>
       </c>
       <c r="T4">
-        <f>(48.01641492+48.55275876+40.54854949)/3</f>
-        <v>45.705907723333333</v>
+        <f>(41.66354431+42.24015674+36.57114211)/3</f>
+        <v>40.158281053333333</v>
       </c>
       <c r="U4">
         <v>456</v>
@@ -1797,50 +1613,50 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>0.70120000000000005</v>
+        <v>0.70330000000000004</v>
       </c>
       <c r="D5">
-        <v>-0.183</v>
+        <v>-0.1855</v>
       </c>
       <c r="E5">
-        <v>0.2155</v>
+        <v>0.22670000000000001</v>
       </c>
       <c r="G5">
-        <v>69.59</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="H5">
-        <v>-0.40139999999999998</v>
+        <v>-0.40539999999999998</v>
       </c>
       <c r="I5">
-        <v>0.40920000000000001</v>
+        <v>0.4073</v>
       </c>
       <c r="K5">
-        <v>3.8030000000000001E-2</v>
+        <v>3.3640000000000003E-2</v>
       </c>
       <c r="L5">
-        <v>-0.4083</v>
+        <v>-0.42970000000000003</v>
       </c>
       <c r="M5">
-        <v>0.34389999999999998</v>
+        <v>0.34789999999999999</v>
       </c>
       <c r="O5">
         <v>0.63</v>
       </c>
       <c r="P5">
-        <v>2.7761000000000002E-4</v>
+        <v>2.8204E-4</v>
       </c>
       <c r="Q5">
-        <v>6.9343740000000001E-2</v>
+        <v>7.019765E-2</v>
       </c>
       <c r="R5">
-        <v>0.25520611999999998</v>
-      </c>
-      <c r="S5" s="2">
-        <v>920</v>
+        <v>0.26619063999999998</v>
+      </c>
+      <c r="S5" s="1">
+        <v>940</v>
       </c>
       <c r="T5">
-        <f>(38.60479803+38.51581893+39.11051392)/3</f>
-        <v>38.743710293333336</v>
+        <f>(39.04959972+38.97188548+36.7339374)/3</f>
+        <v>38.251807533333334</v>
       </c>
       <c r="U5">
         <v>596</v>
@@ -1851,50 +1667,50 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>0.68030000000000002</v>
+        <v>0.67520000000000002</v>
       </c>
       <c r="D6">
-        <v>-0.16250000000000001</v>
+        <v>-0.1628</v>
       </c>
       <c r="E6">
-        <v>0.16420000000000001</v>
+        <v>0.1615</v>
       </c>
       <c r="G6">
-        <v>69.510000000000005</v>
+        <v>69.52</v>
       </c>
       <c r="H6">
-        <v>-0.39079999999999998</v>
+        <v>-0.39560000000000001</v>
       </c>
       <c r="I6">
-        <v>0.40179999999999999</v>
+        <v>0.40289999999999998</v>
       </c>
       <c r="K6">
-        <v>5.9040000000000002E-2</v>
+        <v>6.898E-2</v>
       </c>
       <c r="L6">
-        <v>-0.28460000000000002</v>
+        <v>-0.28199999999999997</v>
       </c>
       <c r="M6">
-        <v>0.2848</v>
+        <v>0.28410000000000002</v>
       </c>
       <c r="O6">
         <v>0.64300000000000002</v>
       </c>
-      <c r="P6" s="2">
-        <v>1.82457804E-4</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>4.5305342700000001E-2</v>
-      </c>
-      <c r="R6" s="2">
-        <v>0.212610469</v>
-      </c>
-      <c r="S6" s="2">
+      <c r="P6" s="1">
+        <v>1.8296731700000001E-4</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>4.5737395799999997E-2</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0.21480924200000001</v>
+      </c>
+      <c r="S6" s="1">
         <v>1200</v>
       </c>
       <c r="T6">
-        <f>(34.42898089+34.37994385+35.57550348)/3</f>
-        <v>34.794809406666666</v>
+        <f>(33.89415722+34.02318876+33.11080822)/3</f>
+        <v>33.676051399999999</v>
       </c>
       <c r="U6">
         <v>662</v>
@@ -1905,50 +1721,50 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>0.76900000000000002</v>
+        <v>0.76459999999999995</v>
       </c>
       <c r="D7">
-        <v>-0.13270000000000001</v>
+        <v>-0.13189999999999999</v>
       </c>
       <c r="E7">
-        <v>0.1283</v>
+        <v>0.12690000000000001</v>
       </c>
       <c r="G7">
         <v>69.599999999999994</v>
       </c>
       <c r="H7">
-        <v>-0.38869999999999999</v>
+        <v>-0.39119999999999999</v>
       </c>
       <c r="I7">
-        <v>0.38640000000000002</v>
+        <v>0.38679999999999998</v>
       </c>
       <c r="K7">
-        <v>-0.11409999999999999</v>
+        <v>-0.10589999999999999</v>
       </c>
       <c r="L7">
-        <v>-0.20949999999999999</v>
+        <v>-0.2079</v>
       </c>
       <c r="M7">
-        <v>0.2195</v>
+        <v>0.22</v>
       </c>
       <c r="O7">
-        <v>0.64700000000000002</v>
-      </c>
-      <c r="P7" s="2">
-        <v>1.4769275000000001E-4</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>3.2447299499999999E-2</v>
-      </c>
-      <c r="R7" s="2">
-        <v>0.18447190499999999</v>
-      </c>
-      <c r="S7" s="2">
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1.5125781700000001E-4</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>3.2074106599999999E-2</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0.185005908</v>
+      </c>
+      <c r="S7" s="1">
         <v>1200</v>
       </c>
       <c r="T7">
-        <f>(37.17488024+37.55674176+32.67860701)/3</f>
-        <v>35.803409670000001</v>
+        <f>(34.5926663+34.52007751+35.68669148)/3</f>
+        <v>34.933145096666664</v>
       </c>
       <c r="U7">
         <v>697</v>
@@ -1959,57 +1775,57 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>0.69820000000000004</v>
+        <v>0.69740000000000002</v>
       </c>
       <c r="D8">
-        <v>-0.11260000000000001</v>
+        <v>-0.1137</v>
       </c>
       <c r="E8">
-        <v>0.108</v>
+        <v>0.1086</v>
       </c>
       <c r="G8">
-        <v>69.510000000000005</v>
+        <v>69.5</v>
       </c>
       <c r="H8">
-        <v>-0.37480000000000002</v>
+        <v>-0.37880000000000003</v>
       </c>
       <c r="I8">
-        <v>0.3745</v>
+        <v>0.38129999999999997</v>
       </c>
       <c r="K8">
-        <v>1.6070000000000001E-2</v>
+        <v>1.452E-2</v>
       </c>
       <c r="L8">
-        <v>-0.1726</v>
+        <v>-0.1704</v>
       </c>
       <c r="M8">
-        <v>0.17799999999999999</v>
+        <v>0.17879999999999999</v>
       </c>
       <c r="O8">
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="P8" s="2">
-        <v>1.3093522600000001E-4</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>2.3918394700000001E-2</v>
-      </c>
-      <c r="R8" s="2">
-        <v>0.16331831799999999</v>
-      </c>
-      <c r="S8" s="2">
-        <v>1200</v>
+        <v>0.64700000000000002</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1.3325364400000001E-4</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>2.3152339899999999E-2</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0.167095786</v>
+      </c>
+      <c r="S8" s="1">
+        <v>1300</v>
       </c>
       <c r="T8">
-        <f>(38.31371612+39.60353928+34.47433264)/3</f>
-        <v>37.463862679999998</v>
+        <f>(35.97857163+35.61775522+34.60117308)/3</f>
+        <v>35.399166643333331</v>
       </c>
       <c r="U8">
         <v>714</v>
       </c>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="S9" s="2"/>
+      <c r="S9" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2184,6 +2000,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="a92532b4-f879-4fe1-8d04-1598af4c66df" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C39779CE51381A47A2D563D620AB4F4F" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9836cfbd5bda03dcca4367e592b7d388">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="a92532b4-f879-4fe1-8d04-1598af4c66df" xmlns:ns4="0e2b3051-a01b-4d08-a066-d3d830b6acb3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f55fd03ad874785ffaac62a1a7ac6935" ns3:_="" ns4:_="">
     <xsd:import namespace="a92532b4-f879-4fe1-8d04-1598af4c66df"/>
@@ -2410,24 +2243,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="a92532b4-f879-4fe1-8d04-1598af4c66df" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A50C4C1D-6D9B-45A9-A99E-05EE4DC1E73B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69BE6D36-C8FF-4779-812D-8A5C120E9773}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="a92532b4-f879-4fe1-8d04-1598af4c66df"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="0e2b3051-a01b-4d08-a066-d3d830b6acb3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{938A1C85-A60A-4083-A756-69973943C621}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2444,29 +2285,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69BE6D36-C8FF-4779-812D-8A5C120E9773}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="0e2b3051-a01b-4d08-a066-d3d830b6acb3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a92532b4-f879-4fe1-8d04-1598af4c66df"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A50C4C1D-6D9B-45A9-A99E-05EE4DC1E73B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>